--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLASS BASQUET SANT ANTONI.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLASS BASQUET SANT ANTONI.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>101.1661</v>
+        <v>79.50410000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>66.58409999999999</v>
+        <v>51.3201</v>
       </c>
       <c r="F2" t="n">
-        <v>34.582</v>
+        <v>28.184</v>
       </c>
       <c r="G2" t="n">
         <v>40.2423</v>
@@ -610,13 +610,13 @@
         <v>45.3804</v>
       </c>
       <c r="S2" t="n">
-        <v>43.36</v>
+        <v>21.6981</v>
       </c>
       <c r="T2" t="n">
-        <v>24.2408</v>
+        <v>8.976599999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>19.1193</v>
+        <v>12.7217</v>
       </c>
       <c r="V2" t="n">
         <v>31.9378</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>48.5151</v>
+        <v>57.4332</v>
       </c>
       <c r="E3" t="n">
-        <v>20.367</v>
+        <v>42.1079</v>
       </c>
       <c r="F3" t="n">
-        <v>28.1479</v>
+        <v>15.3253</v>
       </c>
       <c r="G3" t="n">
-        <v>19.4972</v>
+        <v>34.3077</v>
       </c>
       <c r="H3" t="n">
-        <v>14.3138</v>
+        <v>11.5576</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1834</v>
+        <v>22.7503</v>
       </c>
       <c r="J3" t="n">
-        <v>31.8368</v>
+        <v>53.0816</v>
       </c>
       <c r="K3" t="n">
-        <v>20.4257</v>
+        <v>19.5551</v>
       </c>
       <c r="L3" t="n">
-        <v>11.4109</v>
+        <v>33.5267</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.3395</v>
+        <v>-18.7737</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.1119</v>
+        <v>-7.997300000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.2275</v>
+        <v>-10.7762</v>
       </c>
       <c r="P3" t="n">
-        <v>8.829800000000001</v>
+        <v>-7.1871</v>
       </c>
       <c r="Q3" t="n">
-        <v>-29.7745</v>
+        <v>-45.7913</v>
       </c>
       <c r="R3" t="n">
-        <v>38.6042</v>
+        <v>38.6045</v>
       </c>
       <c r="S3" t="n">
-        <v>21.6479</v>
+        <v>10.1473</v>
       </c>
       <c r="T3" t="n">
-        <v>11.034</v>
+        <v>3.8202</v>
       </c>
       <c r="U3" t="n">
-        <v>10.6134</v>
+        <v>6.3267</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4603</v>
+        <v>20.165</v>
       </c>
       <c r="W3" t="n">
-        <v>7.270600000000001</v>
+        <v>30.9973</v>
       </c>
       <c r="X3" t="n">
-        <v>-8.730600000000001</v>
+        <v>-10.8322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>39.5376</v>
+        <v>49.6579</v>
       </c>
       <c r="E4" t="n">
-        <v>27.3784</v>
+        <v>40.9432</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1593</v>
+        <v>8.7148</v>
       </c>
       <c r="G4" t="n">
-        <v>34.3077</v>
+        <v>42.13180000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>11.5576</v>
+        <v>17.4705</v>
       </c>
       <c r="I4" t="n">
-        <v>22.7503</v>
+        <v>24.6609</v>
       </c>
       <c r="J4" t="n">
-        <v>53.0816</v>
+        <v>57.874</v>
       </c>
       <c r="K4" t="n">
-        <v>19.5551</v>
+        <v>24.2942</v>
       </c>
       <c r="L4" t="n">
-        <v>33.5267</v>
+        <v>33.5801</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.7737</v>
+        <v>-15.7421</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.997300000000001</v>
+        <v>-6.8233</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.7762</v>
+        <v>-8.9184</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.1871</v>
+        <v>-12.5257</v>
       </c>
       <c r="Q4" t="n">
-        <v>-45.7913</v>
+        <v>-48.0497</v>
       </c>
       <c r="R4" t="n">
-        <v>38.6045</v>
+        <v>35.5244</v>
       </c>
       <c r="S4" t="n">
-        <v>-7.7487</v>
+        <v>9.854699999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.9096</v>
+        <v>3.8979</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1607</v>
+        <v>5.9566</v>
       </c>
       <c r="V4" t="n">
-        <v>20.165</v>
+        <v>10.1972</v>
       </c>
       <c r="W4" t="n">
-        <v>30.9973</v>
+        <v>27.221</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.8322</v>
+        <v>-17.0238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>35.6275</v>
+        <v>44.03359999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>32.30759999999999</v>
+        <v>17.419</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3203</v>
+        <v>26.615</v>
       </c>
       <c r="G5" t="n">
-        <v>42.13180000000001</v>
+        <v>19.4972</v>
       </c>
       <c r="H5" t="n">
-        <v>17.4705</v>
+        <v>14.3138</v>
       </c>
       <c r="I5" t="n">
-        <v>24.6609</v>
+        <v>5.1834</v>
       </c>
       <c r="J5" t="n">
-        <v>57.874</v>
+        <v>31.8368</v>
       </c>
       <c r="K5" t="n">
-        <v>24.2942</v>
+        <v>20.4257</v>
       </c>
       <c r="L5" t="n">
-        <v>33.5801</v>
+        <v>11.4109</v>
       </c>
       <c r="M5" t="n">
-        <v>-15.7421</v>
+        <v>-12.3395</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.8233</v>
+        <v>-6.1119</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.9184</v>
+        <v>-6.2275</v>
       </c>
       <c r="P5" t="n">
-        <v>-12.5257</v>
+        <v>8.829800000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-48.0497</v>
+        <v>-29.7745</v>
       </c>
       <c r="R5" t="n">
-        <v>35.5244</v>
+        <v>38.6042</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.1755</v>
+        <v>17.167</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.738</v>
+        <v>8.086</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5620999999999998</v>
+        <v>9.0808</v>
       </c>
       <c r="V5" t="n">
-        <v>10.1972</v>
+        <v>-1.4603</v>
       </c>
       <c r="W5" t="n">
-        <v>27.221</v>
+        <v>7.270600000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.0238</v>
+        <v>-8.730600000000001</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>35.0093</v>
+        <v>28.1753</v>
       </c>
       <c r="E6" t="n">
-        <v>18.0825</v>
+        <v>12.0349</v>
       </c>
       <c r="F6" t="n">
-        <v>16.9269</v>
+        <v>16.1401</v>
       </c>
       <c r="G6" t="n">
         <v>14.3828</v>
@@ -922,13 +922,13 @@
         <v>32.2387</v>
       </c>
       <c r="S6" t="n">
-        <v>23.431</v>
+        <v>16.5968</v>
       </c>
       <c r="T6" t="n">
-        <v>16.8804</v>
+        <v>10.8329</v>
       </c>
       <c r="U6" t="n">
-        <v>6.5507</v>
+        <v>5.764</v>
       </c>
       <c r="V6" t="n">
         <v>-7.116700000000001</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>27.9203</v>
+        <v>13.4826</v>
       </c>
       <c r="E7" t="n">
-        <v>39.9039</v>
+        <v>12.4886</v>
       </c>
       <c r="F7" t="n">
-        <v>-11.9839</v>
+        <v>0.9937999999999996</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.1518</v>
+        <v>1.390000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.4776</v>
+        <v>-9.632300000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.673999999999999</v>
+        <v>11.0225</v>
       </c>
       <c r="J7" t="n">
-        <v>12.7456</v>
+        <v>14.7383</v>
       </c>
       <c r="K7" t="n">
-        <v>7.838799999999999</v>
+        <v>-0.6842000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4.9069</v>
+        <v>15.4222</v>
       </c>
       <c r="M7" t="n">
-        <v>-21.8974</v>
+        <v>-13.3482</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.3165</v>
+        <v>-8.948599999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.5808</v>
+        <v>-4.3996</v>
       </c>
       <c r="P7" t="n">
-        <v>5.3389</v>
+        <v>17.454</v>
       </c>
       <c r="Q7" t="n">
-        <v>-21.1501</v>
+        <v>-9.856400000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>26.4892</v>
+        <v>27.3107</v>
       </c>
       <c r="S7" t="n">
-        <v>38.4196</v>
+        <v>1.563</v>
       </c>
       <c r="T7" t="n">
-        <v>37.9599</v>
+        <v>0.4036</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4597999999999999</v>
+        <v>1.1593</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.6866</v>
+        <v>-6.9245</v>
       </c>
       <c r="W7" t="n">
-        <v>10.3487</v>
+        <v>7.203100000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.0353</v>
+        <v>-14.1277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1708000000000007</v>
+        <v>8.355900000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7264999999999997</v>
+        <v>17.3408</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8976999999999998</v>
+        <v>-8.984999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.210999999999999</v>
+        <v>-9.1518</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3364999999999996</v>
+        <v>-3.4776</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.5473</v>
+        <v>-5.673999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.933800000000001</v>
+        <v>12.7456</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8292</v>
+        <v>7.838799999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.8953</v>
+        <v>4.9069</v>
       </c>
       <c r="M8" t="n">
-        <v>-9.145099999999999</v>
+        <v>-21.8974</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.492599999999999</v>
+        <v>-11.3165</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.6526</v>
+        <v>-10.5808</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2054999999999997</v>
+        <v>5.3389</v>
       </c>
       <c r="Q8" t="n">
-        <v>-13.1418</v>
+        <v>-21.1501</v>
       </c>
       <c r="R8" t="n">
-        <v>12.9363</v>
+        <v>26.4892</v>
       </c>
       <c r="S8" t="n">
-        <v>6.5787</v>
+        <v>18.8554</v>
       </c>
       <c r="T8" t="n">
-        <v>5.647099999999999</v>
+        <v>15.397</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9319000000000002</v>
+        <v>3.4586</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6665999999999999</v>
+        <v>-6.6866</v>
       </c>
       <c r="W8" t="n">
-        <v>6.2872</v>
+        <v>10.3487</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.6205</v>
+        <v>-17.0353</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.502800000000001</v>
+        <v>2.5102</v>
       </c>
       <c r="E9" t="n">
-        <v>3.097499999999999</v>
+        <v>-4.962800000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.600599999999999</v>
+        <v>7.4725</v>
       </c>
       <c r="G9" t="n">
-        <v>1.390000000000001</v>
+        <v>-10.623</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.632300000000001</v>
+        <v>-2.047899999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>11.0225</v>
+        <v>-8.575099999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>14.7383</v>
+        <v>0.3002999999999992</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6842000000000001</v>
+        <v>4.3419</v>
       </c>
       <c r="L9" t="n">
-        <v>15.4222</v>
+        <v>-4.0416</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.3482</v>
+        <v>-10.9235</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.948599999999999</v>
+        <v>-6.3898</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.3996</v>
+        <v>-4.5337</v>
       </c>
       <c r="P9" t="n">
-        <v>17.454</v>
+        <v>9.2403</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.856400000000001</v>
+        <v>-8.2135</v>
       </c>
       <c r="R9" t="n">
-        <v>27.3107</v>
+        <v>17.4542</v>
       </c>
       <c r="S9" t="n">
-        <v>-14.4224</v>
+        <v>3.0858</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.987299999999999</v>
+        <v>1.9893</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.435</v>
+        <v>1.0962</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.9245</v>
+        <v>0.8069999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>7.203100000000001</v>
+        <v>0.9608</v>
       </c>
       <c r="X9" t="n">
-        <v>-14.1277</v>
+        <v>-0.1537999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4653</v>
+        <v>-0.2161999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.4447</v>
+        <v>-2.359500000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9797</v>
+        <v>2.143899999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-10.623</v>
+        <v>8.2462</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.047899999999999</v>
+        <v>8.210899999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.575099999999999</v>
+        <v>0.03569999999999984</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3002999999999992</v>
+        <v>28.4913</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3419</v>
+        <v>18.8843</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.0416</v>
+        <v>9.6073</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.9235</v>
+        <v>-20.2451</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.3898</v>
+        <v>-10.6732</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.5337</v>
+        <v>-9.5715</v>
       </c>
       <c r="P10" t="n">
-        <v>9.2403</v>
+        <v>2.6697</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.2135</v>
+        <v>-36.1401</v>
       </c>
       <c r="R10" t="n">
-        <v>17.4542</v>
+        <v>38.8098</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.8895</v>
+        <v>3.9053</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.4927</v>
+        <v>0.2441999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3972</v>
+        <v>3.6611</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8069999999999999</v>
+        <v>-15.0369</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9608</v>
+        <v>5.044600000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1537999999999999</v>
+        <v>-20.0816</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6648</v>
+        <v>-0.6412000000000004</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0337</v>
+        <v>-0.7496</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6311</v>
+        <v>0.1083999999999998</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4373</v>
+        <v>-7.210999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.003400000000001</v>
+        <v>0.3364999999999996</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4337000000000001</v>
+        <v>-7.5473</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4962</v>
+        <v>1.933800000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.733</v>
+        <v>5.8292</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2369</v>
+        <v>-3.8953</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05890000000000012</v>
+        <v>-9.145099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7295</v>
+        <v>-5.492599999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6705</v>
+        <v>-3.6526</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2321</v>
+        <v>-0.2054999999999997</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1068</v>
+        <v>-13.1418</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8747</v>
+        <v>12.9363</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3227999999999999</v>
+        <v>6.1085</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9801</v>
+        <v>4.171099999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6572</v>
+        <v>1.9378</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.3181</v>
+        <v>0.6665999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5893</v>
+        <v>6.2872</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.9074</v>
+        <v>-5.6205</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.830500000000001</v>
+        <v>-4.8667</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.280099999999999</v>
+        <v>1.614100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.5505</v>
+        <v>-6.4808</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2012</v>
@@ -1390,13 +1390,13 @@
         <v>10.4725</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2824</v>
+        <v>3.6815</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7716</v>
+        <v>1.1227</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4893999999999999</v>
+        <v>2.559</v>
       </c>
       <c r="V12" t="n">
         <v>-6.3735</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.971</v>
+        <v>-8.015600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.5813</v>
+        <v>-6.1772</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.389600000000001</v>
+        <v>-1.8385</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.875</v>
+        <v>-3.4373</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3935</v>
+        <v>-3.003400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.4814</v>
+        <v>-0.4337000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>6.6297</v>
+        <v>-3.4962</v>
       </c>
       <c r="K13" t="n">
-        <v>8.097</v>
+        <v>-3.733</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4675</v>
+        <v>0.2369</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.5047</v>
+        <v>0.05890000000000012</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.4906</v>
+        <v>0.7295</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.0136</v>
+        <v>-0.6705</v>
       </c>
       <c r="P13" t="n">
-        <v>4.1069</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q13" t="n">
-        <v>-28.5423</v>
+        <v>-4.1068</v>
       </c>
       <c r="R13" t="n">
-        <v>32.6496</v>
+        <v>2.8747</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7384</v>
+        <v>-0.02820000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1341</v>
+        <v>0.8368</v>
       </c>
       <c r="U13" t="n">
-        <v>4.8725</v>
+        <v>-0.8646</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.9411</v>
+        <v>-3.3181</v>
       </c>
       <c r="W13" t="n">
-        <v>12.4656</v>
+        <v>0.5893</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.4071</v>
+        <v>-3.9074</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.4656</v>
+        <v>-8.465599999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.9316</v>
+        <v>-8.1762</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5342000000000002</v>
+        <v>-0.2895999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>8.2462</v>
+        <v>-14.875</v>
       </c>
       <c r="H14" t="n">
-        <v>8.210899999999999</v>
+        <v>-2.3935</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03569999999999984</v>
+        <v>-12.4814</v>
       </c>
       <c r="J14" t="n">
-        <v>28.4913</v>
+        <v>6.6297</v>
       </c>
       <c r="K14" t="n">
-        <v>18.8843</v>
+        <v>8.097</v>
       </c>
       <c r="L14" t="n">
-        <v>9.6073</v>
+        <v>-1.4675</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.2451</v>
+        <v>-21.5047</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.6732</v>
+        <v>-10.4906</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.5715</v>
+        <v>-11.0136</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6697</v>
+        <v>4.1069</v>
       </c>
       <c r="Q14" t="n">
-        <v>-36.1401</v>
+        <v>-28.5423</v>
       </c>
       <c r="R14" t="n">
-        <v>38.8098</v>
+        <v>32.6496</v>
       </c>
       <c r="S14" t="n">
-        <v>-11.3446</v>
+        <v>8.2437</v>
       </c>
       <c r="T14" t="n">
-        <v>-12.3275</v>
+        <v>1.2712</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9826000000000001</v>
+        <v>6.9723</v>
       </c>
       <c r="V14" t="n">
-        <v>-15.0369</v>
+        <v>-5.9411</v>
       </c>
       <c r="W14" t="n">
-        <v>5.044600000000001</v>
+        <v>12.4656</v>
       </c>
       <c r="X14" t="n">
-        <v>-20.0816</v>
+        <v>-18.4071</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>232.7050999999999</v>
+        <v>260.9474999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>164.1761</v>
+        <v>172.8433</v>
       </c>
       <c r="F15" t="n">
-        <v>68.52849999999999</v>
+        <v>88.10390000000001</v>
       </c>
       <c r="G15" t="n">
         <v>111.6987</v>
@@ -1612,25 +1612,25 @@
         <v>-92.42489999999998</v>
       </c>
       <c r="O15" t="n">
-        <v>-84.5731</v>
+        <v>-84.57310000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>17.4539</v>
+        <v>17.45390000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-341.8928000000001</v>
+        <v>-341.8928</v>
       </c>
       <c r="R15" t="n">
         <v>359.3492000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>92.63530000000002</v>
+        <v>120.8789</v>
       </c>
       <c r="T15" t="n">
-        <v>52.38149999999997</v>
+        <v>61.04949999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>40.253</v>
+        <v>59.8295</v>
       </c>
       <c r="V15" t="n">
         <v>10.9159</v>
